--- a/public/route-rationalization-kashmir/Kashmir_Route_Frequency_Plan_v3.3.8_RTO.xlsx
+++ b/public/route-rationalization-kashmir/Kashmir_Route_Frequency_Plan_v3.3.8_RTO.xlsx
@@ -15012,7 +15012,7 @@
     <row r="126">
       <c r="A126" s="56" t="inlineStr">
         <is>
-          <t>BGSR02101725</t>
+          <t>BGSR02102163-01</t>
         </is>
       </c>
       <c r="B126" s="56" t="inlineStr">
@@ -15452,7 +15452,7 @@
     <row r="130">
       <c r="A130" s="56" t="inlineStr">
         <is>
-          <t>TMP-K0129</t>
+          <t>BGSR02102163-02</t>
         </is>
       </c>
       <c r="B130" s="56" t="inlineStr">
@@ -15782,7 +15782,7 @@
     <row r="133">
       <c r="A133" s="52" t="inlineStr">
         <is>
-          <t>TMP-K0132</t>
+          <t>BGSR02102163-03</t>
         </is>
       </c>
       <c r="B133" s="52" t="inlineStr">
@@ -18500,7 +18500,7 @@
     <row r="158">
       <c r="A158" s="47" t="inlineStr">
         <is>
-          <t>TMP-K0157</t>
+          <t>SRSR10101834</t>
         </is>
       </c>
       <c r="B158" s="47" t="inlineStr">
@@ -19266,7 +19266,7 @@
     <row r="165">
       <c r="A165" s="56" t="inlineStr">
         <is>
-          <t>SRSR10103460-09</t>
+          <t>BGSR02102163-04</t>
         </is>
       </c>
       <c r="B165" s="56" t="inlineStr">
@@ -37988,7 +37988,7 @@
     <row r="336">
       <c r="A336" s="29" t="inlineStr">
         <is>
-          <t>TMP-K0335</t>
+          <t>BGSR02102163-05</t>
         </is>
       </c>
       <c r="B336" s="29" t="inlineStr">

--- a/public/route-rationalization-kashmir/Kashmir_Route_Frequency_Plan_v3.3.8_RTO.xlsx
+++ b/public/route-rationalization-kashmir/Kashmir_Route_Frequency_Plan_v3.3.8_RTO.xlsx
@@ -2103,7 +2103,7 @@
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>BGSR02102118</t>
+          <t>BGSR02102118A</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
@@ -3603,7 +3603,7 @@
     <row r="21">
       <c r="A21" s="51" t="inlineStr">
         <is>
-          <t>SRSR10101860-01</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B21" s="51" t="inlineStr">
@@ -5331,7 +5331,7 @@
     <row r="37">
       <c r="A37" s="35" t="inlineStr">
         <is>
-          <t>BGSR02102140-01</t>
+          <t>BGSR02102140</t>
         </is>
       </c>
       <c r="B37" s="35" t="inlineStr">
@@ -12299,7 +12299,7 @@
     <row r="101">
       <c r="A101" s="35" t="inlineStr">
         <is>
-          <t>SRSR10100840-01</t>
+          <t>SRSR10102507</t>
         </is>
       </c>
       <c r="B101" s="35" t="inlineStr">
@@ -12625,7 +12625,7 @@
     <row r="104">
       <c r="A104" s="47" t="inlineStr">
         <is>
-          <t>SRSR10100840-02</t>
+          <t>SRSR10100840</t>
         </is>
       </c>
       <c r="B104" s="47" t="inlineStr">
@@ -17665,7 +17665,7 @@
     <row r="150">
       <c r="A150" s="47" t="inlineStr">
         <is>
-          <t>BGSR02102140-02</t>
+          <t>SRSR10101808</t>
         </is>
       </c>
       <c r="B150" s="47" t="inlineStr">
@@ -18647,7 +18647,7 @@
     <row r="159">
       <c r="A159" s="35" t="inlineStr">
         <is>
-          <t>SRSR10101860-02</t>
+          <t>SRSR10102462</t>
         </is>
       </c>
       <c r="B159" s="35" t="inlineStr">
@@ -18863,7 +18863,7 @@
     <row r="161">
       <c r="A161" s="51" t="inlineStr">
         <is>
-          <t>SRSR10100840-03</t>
+          <t>BGSR02102124</t>
         </is>
       </c>
       <c r="B161" s="51" t="inlineStr">
@@ -19079,7 +19079,7 @@
     <row r="163">
       <c r="A163" s="56" t="inlineStr">
         <is>
-          <t>SRPW10086005</t>
+          <t>BGSR02102124</t>
         </is>
       </c>
       <c r="B163" s="56" t="inlineStr">
@@ -30031,7 +30031,7 @@
     <row r="263">
       <c r="A263" s="41" t="inlineStr">
         <is>
-          <t>BGSP02092119</t>
+          <t>SRSR10102507</t>
         </is>
       </c>
       <c r="B263" s="41" t="inlineStr">
@@ -39805,7 +39805,7 @@
     <row r="352">
       <c r="A352" s="41" t="inlineStr">
         <is>
-          <t>TMP-K0351</t>
+          <t>SRSR10102507</t>
         </is>
       </c>
       <c r="B352" s="41" t="inlineStr">
@@ -60241,7 +60241,7 @@
     <row r="540">
       <c r="A540" s="56" t="inlineStr">
         <is>
-          <t>TMP-K0539</t>
+          <t>ANAN01010101</t>
         </is>
       </c>
       <c r="B540" s="56" t="inlineStr">
@@ -65999,7 +65999,7 @@
     <row r="593">
       <c r="A593" s="35" t="inlineStr">
         <is>
-          <t>SRSR10100808-01</t>
+          <t>SRBG10020918</t>
         </is>
       </c>
       <c r="B593" s="35" t="inlineStr">
@@ -66423,7 +66423,7 @@
     <row r="597">
       <c r="A597" s="35" t="inlineStr">
         <is>
-          <t>SRBG10024017</t>
+          <t>SRBG10024017B</t>
         </is>
       </c>
       <c r="B597" s="35" t="inlineStr">
@@ -66635,7 +66635,7 @@
     <row r="599">
       <c r="A599" s="51" t="inlineStr">
         <is>
-          <t>SRBG10020904-01</t>
+          <t>SRBG10020904A</t>
         </is>
       </c>
       <c r="B599" s="51" t="inlineStr">
@@ -66741,7 +66741,7 @@
     <row r="600">
       <c r="A600" s="47" t="inlineStr">
         <is>
-          <t>SRSR10105418</t>
+          <t>BGSR02102118B</t>
         </is>
       </c>
       <c r="B600" s="47" t="inlineStr">
@@ -66847,7 +66847,7 @@
     <row r="601">
       <c r="A601" s="35" t="inlineStr">
         <is>
-          <t>SRBG10024005</t>
+          <t>SRBG10024017A</t>
         </is>
       </c>
       <c r="B601" s="35" t="inlineStr">
@@ -66953,7 +66953,7 @@
     <row r="602">
       <c r="A602" s="47" t="inlineStr">
         <is>
-          <t>SRSR10104242</t>
+          <t>SRSR10103761</t>
         </is>
       </c>
       <c r="B602" s="47" t="inlineStr">
@@ -67483,7 +67483,7 @@
     <row r="607">
       <c r="A607" s="35" t="inlineStr">
         <is>
-          <t>SRSR10100808-02</t>
+          <t>SRSR10100940</t>
         </is>
       </c>
       <c r="B607" s="35" t="inlineStr">
@@ -67695,7 +67695,7 @@
     <row r="609">
       <c r="A609" s="35" t="inlineStr">
         <is>
-          <t>SRBG10022505</t>
+          <t>SRSR10106005</t>
         </is>
       </c>
       <c r="B609" s="35" t="inlineStr">
@@ -68013,7 +68013,7 @@
     <row r="612">
       <c r="A612" s="47" t="inlineStr">
         <is>
-          <t>SRBG10020802</t>
+          <t>SRSR10100965</t>
         </is>
       </c>
       <c r="B612" s="47" t="inlineStr">
@@ -68225,7 +68225,7 @@
     <row r="614">
       <c r="A614" s="60" t="inlineStr">
         <is>
-          <t>SRBG10020807</t>
+          <t>SRBG10020907</t>
         </is>
       </c>
       <c r="B614" s="60" t="inlineStr">
@@ -68331,7 +68331,7 @@
     <row r="615">
       <c r="A615" s="35" t="inlineStr">
         <is>
-          <t>SRBR10044003</t>
+          <t>SRBR10044010</t>
         </is>
       </c>
       <c r="B615" s="35" t="inlineStr">
@@ -68437,7 +68437,7 @@
     <row r="616">
       <c r="A616" s="47" t="inlineStr">
         <is>
-          <t>SRPW10080813</t>
+          <t>SRPW10080913</t>
         </is>
       </c>
       <c r="B616" s="47" t="inlineStr">
@@ -68543,7 +68543,7 @@
     <row r="617">
       <c r="A617" s="66" t="inlineStr">
         <is>
-          <t>SRGB10050804-01</t>
+          <t>SRSR10100955A</t>
         </is>
       </c>
       <c r="B617" s="66" t="inlineStr">
@@ -68649,7 +68649,7 @@
     <row r="618">
       <c r="A618" s="66" t="inlineStr">
         <is>
-          <t>SRGB10050804-02</t>
+          <t>SRSR10100955B</t>
         </is>
       </c>
       <c r="B618" s="66" t="inlineStr">
@@ -68861,7 +68861,7 @@
     <row r="620">
       <c r="A620" s="47" t="inlineStr">
         <is>
-          <t>SRSR10104039</t>
+          <t>SRBG10024014</t>
         </is>
       </c>
       <c r="B620" s="47" t="inlineStr">
@@ -68967,7 +68967,7 @@
     <row r="621">
       <c r="A621" s="51" t="inlineStr">
         <is>
-          <t>SRBG10020904-02</t>
+          <t>SRBG10020904B</t>
         </is>
       </c>
       <c r="B621" s="51" t="inlineStr">
